--- a/christmas_forms/020_santa_breakfast_participation_survey--christmas_forms.xlsx
+++ b/christmas_forms/020_santa_breakfast_participation_survey--christmas_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -437,12 +437,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E28"/>
+  <dimension ref="A1:E21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="17" customWidth="1" min="1" max="1"/>
+    <col width="12" customWidth="1" min="1" max="1"/>
     <col width="21" customWidth="1" min="2" max="2"/>
-    <col width="21" customWidth="1" min="3" max="3"/>
+    <col width="50" customWidth="1" min="3" max="3"/>
     <col width="6" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
   </cols>
@@ -525,13 +525,13 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>participant_info</t>
+          <t>What is your name?</t>
         </is>
       </c>
       <c r="D4" t="inlineStr"/>
       <c r="E4" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -543,12 +543,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>school_name</t>
+          <t>school_details</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>school_name</t>
+          <t>Which school did you attend?</t>
         </is>
       </c>
       <c r="D5" t="inlineStr"/>
@@ -571,13 +571,13 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>event_date</t>
+          <t>When was the event held?</t>
         </is>
       </c>
       <c r="D6" t="inlineStr"/>
       <c r="E6" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -594,36 +594,36 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>event_time</t>
+          <t>What time did you attend the event?</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
       <c r="E7" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>note</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>feedback</t>
+          <t>event_satisfaction</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>feedback</t>
+          <t>How satisfied were you with the event?</t>
         </is>
       </c>
       <c r="D8" t="inlineStr"/>
       <c r="E8" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -635,12 +635,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>email</t>
+          <t>additional_comments</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>email</t>
+          <t>Do you have any additional comments or suggestions?</t>
         </is>
       </c>
       <c r="D9" t="inlineStr"/>
@@ -658,12 +658,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>phone</t>
+          <t>tool_assignment</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>phone</t>
+          <t>What tools were assigned to you during the event?</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
@@ -676,46 +676,46 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>select_one</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>event_attended</t>
+          <t>output_file_name</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>attended_event</t>
+          <t>What is the name of the output file?</t>
         </is>
       </c>
       <c r="D11" t="inlineStr"/>
       <c r="E11" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>no</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>select_multiple</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>attended_with</t>
+          <t>form_id</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>attended_with</t>
+          <t>What is the form ID?</t>
         </is>
       </c>
       <c r="D12" t="inlineStr"/>
       <c r="E12" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>no</t>
         </is>
       </c>
     </row>
@@ -727,12 +727,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>event_satisfaction</t>
+          <t>form_category</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>event_satisfaction</t>
+          <t>What is the category of this form?</t>
         </is>
       </c>
       <c r="D13" t="inlineStr"/>
@@ -750,12 +750,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>event_improvement</t>
+          <t>form_description</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>event_improvement</t>
+          <t>What is the description of this form?</t>
         </is>
       </c>
       <c r="D14" t="inlineStr"/>
@@ -768,17 +768,17 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>note</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>additional_comments</t>
+          <t>form_creator</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>additional_comments</t>
+          <t>Who created this form?</t>
         </is>
       </c>
       <c r="D15" t="inlineStr"/>
@@ -796,12 +796,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>assigned_tool</t>
+          <t>output_file</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>assigned_tool</t>
+          <t>What is the output file?</t>
         </is>
       </c>
       <c r="D16" t="inlineStr"/>
@@ -819,12 +819,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>output_file_name</t>
+          <t>input_schema</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>output_file_name</t>
+          <t>What is the input schema for this form?</t>
         </is>
       </c>
       <c r="D17" t="inlineStr"/>
@@ -842,12 +842,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>form_id</t>
+          <t>form_id_number</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>form_id</t>
+          <t>Form Id Number</t>
         </is>
       </c>
       <c r="D18" t="inlineStr"/>
@@ -860,23 +860,23 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>form_title</t>
+          <t>attended_with</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>form_title</t>
+          <t>Were you attending the event with someone else?</t>
         </is>
       </c>
       <c r="D19" t="inlineStr"/>
       <c r="E19" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -888,12 +888,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>form_category</t>
+          <t>event_rating</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>form_category</t>
+          <t>How would you rate the event?</t>
         </is>
       </c>
       <c r="D20" t="inlineStr"/>
@@ -911,177 +911,16 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>form_description</t>
+          <t>event_comments</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>form_description</t>
+          <t>Do you have any additional comments about the event?</t>
         </is>
       </c>
       <c r="D21" t="inlineStr"/>
       <c r="E21" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>description</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>description</t>
-        </is>
-      </c>
-      <c r="D22" t="inlineStr"/>
-      <c r="E22" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>assigned_tool</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>assigned_tool</t>
-        </is>
-      </c>
-      <c r="D23" t="inlineStr"/>
-      <c r="E23" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>created_by</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>created_by</t>
-        </is>
-      </c>
-      <c r="D24" t="inlineStr"/>
-      <c r="E24" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>output_file_name</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>output_file_name</t>
-        </is>
-      </c>
-      <c r="D25" t="inlineStr"/>
-      <c r="E25" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>output_file</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>output_file</t>
-        </is>
-      </c>
-      <c r="D26" t="inlineStr"/>
-      <c r="E26" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>input_schema</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>input_schema</t>
-        </is>
-      </c>
-      <c r="D27" t="inlineStr"/>
-      <c r="E27" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>form_id</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>form_id</t>
-        </is>
-      </c>
-      <c r="D28" t="inlineStr"/>
-      <c r="E28" t="inlineStr">
         <is>
           <t>no</t>
         </is>
@@ -1098,12 +937,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C17"/>
+  <dimension ref="A1:C19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
-    <col width="22" customWidth="1" min="2" max="2"/>
-    <col width="22" customWidth="1" min="3" max="3"/>
+    <col width="19" customWidth="1" min="2" max="2"/>
+    <col width="19" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1126,272 +965,306 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>school_name_choices</t>
+          <t>school_details_choices</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>school_of_santa</t>
+          <t>santa_school</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>School of Santa</t>
+          <t>Santa School</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>school_name_choices</t>
+          <t>school_details_choices</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>nonprofit</t>
+          <t>community_school</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Nonprofit</t>
+          <t>Community School</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>school_name_choices</t>
+          <t>school_details_choices</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>community_organizers</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Community Organizers</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>event_attended_choices</t>
+          <t>event_satisfaction_choices</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>true</t>
+          <t>very_satisfied</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>Very Satisfied</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>event_attended_choices</t>
+          <t>event_satisfaction_choices</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>false</t>
+          <t>satisfied</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>Satisfied</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>attended_with_choices</t>
+          <t>event_satisfaction_choices</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>family</t>
+          <t>neutral</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Family</t>
+          <t>Neutral</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>attended_with_choices</t>
+          <t>event_satisfaction_choices</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>friends</t>
+          <t>dissatisfied</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Friends</t>
+          <t>Dissatisfied</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>attended_with_choices</t>
+          <t>event_satisfaction_choices</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>alone</t>
+          <t>very_dissatisfied</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Alone</t>
+          <t>Very Dissatisfied</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>event_satisfaction_choices</t>
+          <t>form_category_choices</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>very_satisfied</t>
+          <t>christmas_forms</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Very Satisfied</t>
+          <t>Christmas Forms</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>event_satisfaction_choices</t>
+          <t>form_category_choices</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>satisfied</t>
+          <t>nonprofit_forms</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Satisfied</t>
+          <t>Nonprofit Forms</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>event_satisfaction_choices</t>
+          <t>form_category_choices</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>neutral</t>
+          <t>holiday_forms</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Neutral</t>
+          <t>Holiday Forms</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>event_satisfaction_choices</t>
+          <t>attended_with_choices</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>dissatisfied</t>
+          <t>true</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Dissatisfied</t>
+          <t>True</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>event_satisfaction_choices</t>
+          <t>attended_with_choices</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>very_dissatisfied</t>
+          <t>false</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Very Dissatisfied</t>
+          <t>False</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>form_category_choices</t>
+          <t>event_rating_choices</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>christmas_forms</t>
+          <t>excellent</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Christmas Forms</t>
+          <t>Excellent</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>form_category_choices</t>
+          <t>event_rating_choices</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>nonprofit_forms</t>
+          <t>good</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Nonprofit Forms</t>
+          <t>Good</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>form_category_choices</t>
+          <t>event_rating_choices</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>holiday_forms</t>
+          <t>fair</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Holiday Forms</t>
+          <t>Fair</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>event_rating_choices</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>poor</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Poor</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>event_rating_choices</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>terrible</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Terrible</t>
         </is>
       </c>
     </row>
